--- a/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
+++ b/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,8 +130,44 @@
       <color rgb="002E7D32"/>
       <sz val="9"/>
     </font>
+    <font/>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -176,6 +212,71 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00A86B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9F2E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F4FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF001F5B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0392B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8ECF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE67E22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A56DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B2A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFAFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -249,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -345,6 +446,86 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,6 +600,396 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MarginCOS</author>
+  </authors>
+  <commentList>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>Lane ID
+──────────────────────────────
+Unique identifier for this lane. Must not be duplicated.
+Format: Text
+Example: LN-001
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>Lane Name
+──────────────────────────────
+Descriptive route name (origin – destination).
+Format: Text
+Example: Lagos–Kano
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>Route Region
+──────────────────────────────
+Corridor classification. Must match Reference_Lists exactly.
+Format: Select from dropdown
+Example: Lagos-North · South-South · North-Central
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0">
+      <text>
+        <t>Cargo Type
+──────────────────────────────
+Type of cargo carried. Must match Reference_Lists.
+Format: Select from dropdown
+Example: General Cargo · Cold Chain · Container (20ft)
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <t>Fleet Division
+──────────────────────────────
+Internal fleet division or cost centre name.
+Format: Text
+Example: Northern Fleet · FCT Fleet
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <t>Active (Y/N)
+──────────────────────────────
+Include this lane in analysis? Y = active · N = excluded.
+Format: Y or N
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0" shapeId="0">
+      <text>
+        <t>Contracted Rate (₦)
+──────────────────────────────
+Agreed rate per trip with the client, in Naira. No commas.
+Format: Number &gt; 0
+Example: 1360000
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0" shapeId="0">
+      <text>
+        <t>Fully-Loaded Cost (₦)
+──────────────────────────────
+Total all-in cost per trip: fuel + driver + maintenance + tolls + overheads.
+In Naira. No commas.
+Format: Number &gt; 0
+Example: 1020000
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0" shapeId="0">
+      <text>
+        <t>Distance (km)
+──────────────────────────────
+One-way route distance in kilometres.
+Format: Number &gt; 0
+Example: 1080
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="J4" authorId="0" shapeId="0">
+      <text>
+        <t>Market Rate (₦)
+──────────────────────────────
+Current spot or market rate for this lane, in Naira.
+If known, improves P1 headroom calculation.
+Format: Number &gt; 0
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>Rate Sensitivity
+──────────────────────────────
+Elasticity: % change in trips per 1% rate change. Negative.
+Format: Decimal (e.g. -0.30 = moderate sensitivity)
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="0" shapeId="0">
+      <text>
+        <t>Proposed Rate Chg %
+──────────────────────────────
+Intended rate adjustment as a DECIMAL.
+Format: Decimal (0.05 = 5% increase)
+⚠ Do NOT enter 5 — enter 0.05
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="M4" authorId="0" shapeId="0">
+      <text>
+        <t>Min Margin Floor %
+──────────────────────────────
+Minimum acceptable margin for this lane as a DECIMAL.
+Format: Decimal (0.20 = 20% floor)
+⚠ Do NOT enter 20 — enter 0.20
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0">
+      <text>
+        <t>Rate Headroom %
+──────────────────────────────
+Estimated room to raise rate above contracted level, as a DECIMAL.
+Format: Decimal (0.03 = 3% headroom)
+⚠ Do NOT enter 3 — enter 0.03
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="O4" authorId="0" shapeId="0">
+      <text>
+        <t>Return Lane ID
+──────────────────────────────
+Lane ID of the paired return leg, for backhaul pairing analysis.
+Format: Text (must match a lane_id in another row)
+Example: LN-002
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0" shapeId="0">
+      <text>
+        <t>Backhaul Rate (₦)
+──────────────────────────────
+Revenue earned on the return leg, in Naira.
+Format: Number
+Example: 860000
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="Q4" authorId="0" shapeId="0">
+      <text>
+        <t>Backhaul Cost (₦)
+──────────────────────────────
+Cost of the return leg, in Naira.
+Format: Number
+Example: 680000
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="R4" authorId="0" shapeId="0">
+      <text>
+        <t>Backhaul Recovery %
+──────────────────────────────
+Percentage of return trips carrying paying cargo, as a DECIMAL.
+Format: Decimal (0.65 = 65% utilisation)
+⚠ Do NOT enter 65 — enter 0.65
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="S4" authorId="0" shapeId="0">
+      <text>
+        <t>Fuel Cost/km (₦)
+──────────────────────────────
+Diesel cost per kilometre in Naira.
+Format: Number
+Example: 480
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="T4" authorId="0" shapeId="0">
+      <text>
+        <t>Driver Cost/Trip (₦)
+──────────────────────────────
+Driver wages and per diem per trip, in Naira.
+Format: Number
+Example: 85000
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="U4" authorId="0" shapeId="0">
+      <text>
+        <t>Maintenance/Trip (₦)
+──────────────────────────────
+Tyre, servicing and depreciation cost per trip, in Naira.
+Format: Number
+Example: 62000
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0" shapeId="0">
+      <text>
+        <t>Tolls &amp; Levies/Trip (₦)
+──────────────────────────────
+Checkpoint fees, state levies and park fees per trip, in Naira.
+Format: Number
+Example: 22000
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="W4" authorId="0" shapeId="0">
+      <text>
+        <t>Cost Inflation %
+──────────────────────────────
+Year-on-year operating cost increase as a DECIMAL.
+Format: Decimal (0.18 = 18% inflation)
+⚠ Do NOT enter 18 — enter 0.18
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="X4" authorId="0" shapeId="0">
+      <text>
+        <t>Rate Recovery %
+──────────────────────────────
+Proportion of cost increases recovered via rate adjustment, as a DECIMAL.
+Format: Decimal (0.60 = 60% recovered)
+⚠ Do NOT enter 60 — enter 0.60
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="Y4" authorId="0" shapeId="0">
+      <text>
+        <t>Prior Period Cost (₦)
+──────────────────────────────
+Fully-loaded cost per trip in the previous period, in Naira.
+Used to calculate actual cost movement over time.
+Format: Number
+Example: 865000
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="Z4" authorId="0" shapeId="0">
+      <text>
+        <t>FX Exposure %
+──────────────────────────────
+Percentage of operating costs linked to FX (diesel, imported parts), as a DECIMAL.
+Format: Decimal (0.28 = 28% FX-linked)
+⚠ Do NOT enter 28 — enter 0.28
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AA4" authorId="0" shapeId="0">
+      <text>
+        <t>Truck ID
+──────────────────────────────
+Asset registration number or fleet identifier.
+Format: Text
+Example: TRK-045
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AB4" authorId="0" shapeId="0">
+      <text>
+        <t>Truck Type
+──────────────────────────────
+Vehicle class. Must match Reference_Lists.
+Format: Select from dropdown
+Example: 30-Tonne · Refrigerated · Flatbed · Tanker
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AC4" authorId="0" shapeId="0">
+      <text>
+        <t>Contract Type
+──────────────────────────────
+Commercial arrangement type. Must match Reference_Lists.
+Format: Select from dropdown
+Options: Spot · Dedicated · Contracted · Ad-hoc · Backhaul · Inter-modal
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="AD4" authorId="0" shapeId="0">
+      <text>
+        <t>Customer
+──────────────────────────────
+Shipper or client name.
+Format: Text
+Example: Dangote Industries · Nestlé Nigeria
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AE4" authorId="0" shapeId="0">
+      <text>
+        <t>Customer Margin %
+──────────────────────────────
+Customer contribution margin allocation as a DECIMAL.
+Format: Decimal (0.08 = 8%)
+⚠ Do NOT enter 8 — enter 0.08
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AF4" authorId="0" shapeId="0">
+      <text>
+        <t>Rebate %
+──────────────────────────────
+Volume rebate percentage as a DECIMAL.
+Format: Decimal (0.015 = 1.5%)
+⚠ Do NOT enter 1.5 — enter 0.015
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AG4" authorId="0" shapeId="0">
+      <text>
+        <t>Payment Terms (Days)
+──────────────────────────────
+Standard payment cycle in days.
+Format: Whole number
+Example: 30
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AH4" authorId="0" shapeId="0">
+      <text>
+        <t>Fuel Surcharge Clause
+──────────────────────────────
+Does the contract include automatic fuel surcharge passthrough?
+Format: Select from dropdown
+Options: Yes · No · Partial
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AI4" authorId="0" shapeId="0">
+      <text>
+        <t>Monthly Trips
+──────────────────────────────
+Average number of trips on this lane per month.
+Format: Whole number &gt; 0
+Example: 14
+Required: YES</t>
+      </text>
+    </comment>
+    <comment ref="AJ4" authorId="0" shapeId="0">
+      <text>
+        <t>Discount Depth %
+──────────────────────────────
+Volume discount offered as a DECIMAL.
+Format: Decimal (0.08 = 8% discount)
+⚠ Do NOT enter 8 — enter 0.08
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AK4" authorId="0" shapeId="0">
+      <text>
+        <t>Volume Response %
+──────────────────────────────
+Expected % volume change from rate adjustment, as a DECIMAL.
+Format: Decimal (0.12 = 12% uplift)
+⚠ Do NOT enter 12 — enter 0.12
+Required: NO</t>
+      </text>
+    </comment>
+    <comment ref="AL4" authorId="0" shapeId="0">
+      <text>
+        <t>Operating Region
+──────────────────────────────
+Primary operating hub region. Must match Reference_Lists.
+Format: Select from dropdown
+Example: Lagos · Kano · Abuja · Port Harcourt
+Required: NO</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -710,126 +1281,252 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C19"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="8" customHeight="1"/>
-    <row r="2" ht="32" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>MarginCOS — Logistics Data Template v3.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Lane-level cost floor &amp; margin intelligence</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="26" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>→  Go to the  Lane Data  tab to enter your lane portfolio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="10" customHeight="1"/>
-    <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>HOW TO USE THIS TEMPLATE</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>1.  Enter one row per lane. Each unique Lane ID + Period combination is a snapshot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>2.  Required fields (REQ) must be filled for the row to import. Optional fields unlock deeper analytics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>3.  Use the dropdowns in Route Region, Cargo Type, Contract Type, and Truck Type columns — only listed values will import.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>4.  Enter monetary values in full Naira (₦) — no commas, no currency symbols.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>5.  Enter percentages as numbers (e.g. 18 for 18%, not 0.18).</t>
-        </is>
-      </c>
+    <row r="1" ht="7.5" customHeight="1">
+      <c r="A1" s="35" t="n"/>
+      <c r="B1" s="35" t="n"/>
+      <c r="C1" s="35" t="n"/>
+    </row>
+    <row r="2" ht="31.5" customHeight="1">
+      <c r="A2" s="35" t="n"/>
+      <c r="B2" s="36" t="inlineStr">
+        <is>
+          <t>MarginCOS  ·  CLIENT DATA TEMPLATE  ·  v3.2</t>
+        </is>
+      </c>
+      <c r="E2" s="37" t="inlineStr">
+        <is>
+          <t>VERTICAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="35" t="n"/>
+      <c r="B3" s="38" t="inlineStr">
+        <is>
+          <t>Margin Recovery Intelligence Engine  ·  Powered by Carthena Advisory</t>
+        </is>
+      </c>
+      <c r="E3" s="39" t="inlineStr">
+        <is>
+          <t>LOGISTICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="35" t="n"/>
+      <c r="B4" s="40" t="inlineStr">
+        <is>
+          <t>Complete this file and upload it to margincos.com to generate your lane-level margin and cost floor analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="7.5" customHeight="1">
+      <c r="A5" s="35" t="n"/>
+      <c r="B5" s="35" t="n"/>
+      <c r="C5" s="35" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="n"/>
+      <c r="B6" s="35" t="n"/>
+      <c r="C6" s="35" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="35" t="n"/>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>COLOUR GUIDE</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="n"/>
+    </row>
+    <row r="8" ht="15.8" customHeight="1">
+      <c r="A8" s="35" t="n"/>
+      <c r="B8" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sample</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>REQUIRED FIELD - Must be completed. Upload will fail if blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.8" customHeight="1">
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sample</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>OPTIONAL FIELD - Leave blank to use platform defaults. Completing improves accuracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.8" customHeight="1">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sample</t>
+        </is>
+      </c>
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>DO NOT EDIT - System-generated or formula column. Do not modify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15.8" customHeight="1">
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sample</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>FORMULA COLUMN - Calculates automatically from your inputs. Do not overwrite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="35" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>6.  Save the file and upload it in MarginCOS › Portfolio Manager › Import Data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="8" customHeight="1">
-      <c r="B14" s="6" t="inlineStr"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>REQUIRED FIELDS (minimum for a valid import row)</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>lane_id  ·  lane_name  ·  route_region  ·  cargo_type  ·  active  ·  contracted_rate_ngn  ·  fully_loaded_cost_ngn  ·  distance_km  ·  contract_type  ·  monthly_trips</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="8" customHeight="1">
-      <c r="B17" s="6" t="inlineStr"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>CONTACT</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Support: info@carthenaadvisory.com   |   www.margincos.com</t>
+      <c r="A13" s="35" t="n"/>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HOW TO COMPLETE THIS TEMPLATE</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="n"/>
+    </row>
+    <row r="14" ht="15.8" customHeight="1">
+      <c r="A14" s="35" t="n"/>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>STEP 1</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>Go to the 'Lane Data' sheet. Each row is one lane. This template supports up to 49 lanes per upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>STEP 2</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>Complete all REQUIRED (yellow) fields for every lane. Incomplete required fields will cause the upload to fail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>STEP 3</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>Complete as many OPTIONAL (green) fields as possible. The more you fill in, the richer your cost floor and margin analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>STEP 4</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>Use the 'Reference_Lists' sheet to find valid values for Route Region, Cargo Type, Contract Type, Truck Type, and Operating Region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="41" t="inlineStr">
+        <is>
+          <t>STEP 5</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>Enter ALL percentages as DECIMALS (e.g. 0.18 for 18%, 0.40 for 40%). Do NOT enter 18 or 40 — the platform expects decimals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>STEP 6</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>Save the file and upload at margincos.com → Dashboard → Upload Data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>STEP 7</t>
+        </is>
+      </c>
+      <c r="C20" s="48" t="inlineStr">
+        <is>
+          <t>The platform will validate your data and show an Upload Report before any analysis is generated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NEED HELP?</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Contact your Carthena Advisory engagement manager or email info@carthenaadvisory.com  |  www.margincos.com</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1574,13 +2271,13 @@
         <v>-0.3</v>
       </c>
       <c r="L5" s="19" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="M5" s="19" t="n">
-        <v>20</v>
+        <v>0.2</v>
       </c>
       <c r="N5" s="19" t="n">
-        <v>3</v>
+        <v>0.03</v>
       </c>
       <c r="O5" s="18" t="inlineStr">
         <is>
@@ -1594,7 +2291,7 @@
         <v>680000</v>
       </c>
       <c r="R5" s="19" t="n">
-        <v>65</v>
+        <v>0.65</v>
       </c>
       <c r="S5" s="19" t="n">
         <v>480</v>
@@ -1609,16 +2306,16 @@
         <v>22000</v>
       </c>
       <c r="W5" s="19" t="n">
-        <v>18</v>
+        <v>0.18</v>
       </c>
       <c r="X5" s="19" t="n">
-        <v>60</v>
+        <v>0.6</v>
       </c>
       <c r="Y5" s="19" t="n">
         <v>865000</v>
       </c>
       <c r="Z5" s="19" t="n">
-        <v>28</v>
+        <v>0.28</v>
       </c>
       <c r="AA5" s="18" t="inlineStr">
         <is>
@@ -1641,10 +2338,10 @@
         </is>
       </c>
       <c r="AE5" s="19" t="n">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="AF5" s="19" t="n">
-        <v>1.5</v>
+        <v>0.015</v>
       </c>
       <c r="AG5" s="19" t="n">
         <v>30</v>
@@ -1716,13 +2413,13 @@
         <v>-0.25</v>
       </c>
       <c r="L6" s="21" t="n">
-        <v>3</v>
+        <v>0.03</v>
       </c>
       <c r="M6" s="21" t="n">
-        <v>18</v>
+        <v>0.18</v>
       </c>
       <c r="N6" s="21" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="O6" s="20" t="inlineStr">
         <is>
@@ -1745,16 +2442,16 @@
         <v>22000</v>
       </c>
       <c r="W6" s="21" t="n">
-        <v>18</v>
+        <v>0.18</v>
       </c>
       <c r="X6" s="21" t="n">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="Y6" s="21" t="n">
         <v>610000</v>
       </c>
       <c r="Z6" s="21" t="n">
-        <v>28</v>
+        <v>0.28</v>
       </c>
       <c r="AA6" s="20" t="inlineStr">
         <is>
@@ -1777,10 +2474,10 @@
         </is>
       </c>
       <c r="AE6" s="21" t="n">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="AF6" s="21" t="n">
-        <v>1.5</v>
+        <v>0.015</v>
       </c>
       <c r="AG6" s="21" t="n">
         <v>30</v>
@@ -1852,13 +2549,13 @@
         <v>-0.4</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>20</v>
+        <v>0.2</v>
       </c>
       <c r="N7" s="19" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="O7" s="18" t="n"/>
       <c r="P7" s="23" t="n"/>
@@ -1877,16 +2574,16 @@
         <v>12000</v>
       </c>
       <c r="W7" s="19" t="n">
-        <v>18</v>
+        <v>0.18</v>
       </c>
       <c r="X7" s="19" t="n">
-        <v>55</v>
+        <v>0.55</v>
       </c>
       <c r="Y7" s="19" t="n">
         <v>390000</v>
       </c>
       <c r="Z7" s="19" t="n">
-        <v>32</v>
+        <v>0.32</v>
       </c>
       <c r="AA7" s="18" t="inlineStr">
         <is>
@@ -1909,7 +2606,7 @@
         </is>
       </c>
       <c r="AE7" s="19" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="AF7" s="19" t="n">
         <v>0</v>
@@ -1926,10 +2623,10 @@
         <v>22</v>
       </c>
       <c r="AJ7" s="19" t="n">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="AK7" s="19" t="n">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="AL7" s="18" t="inlineStr">
         <is>
@@ -1984,13 +2681,13 @@
         <v>-0.2</v>
       </c>
       <c r="L8" s="21" t="n">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="M8" s="21" t="n">
-        <v>15</v>
+        <v>0.15</v>
       </c>
       <c r="N8" s="21" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="O8" s="20" t="n"/>
       <c r="P8" s="21" t="n">
@@ -2000,7 +2697,7 @@
         <v>155000</v>
       </c>
       <c r="R8" s="21" t="n">
-        <v>80</v>
+        <v>0.8</v>
       </c>
       <c r="S8" s="21" t="n">
         <v>480</v>
@@ -2015,16 +2712,16 @@
         <v>4500</v>
       </c>
       <c r="W8" s="21" t="n">
-        <v>18</v>
+        <v>0.18</v>
       </c>
       <c r="X8" s="21" t="n">
-        <v>70</v>
+        <v>0.7</v>
       </c>
       <c r="Y8" s="21" t="n">
         <v>165000</v>
       </c>
       <c r="Z8" s="21" t="n">
-        <v>15</v>
+        <v>0.15</v>
       </c>
       <c r="AA8" s="20" t="inlineStr">
         <is>
@@ -2047,10 +2744,10 @@
         </is>
       </c>
       <c r="AE8" s="21" t="n">
-        <v>6</v>
+        <v>0.06</v>
       </c>
       <c r="AF8" s="21" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="AG8" s="21" t="n">
         <v>30</v>
@@ -2064,10 +2761,10 @@
         <v>36</v>
       </c>
       <c r="AJ8" s="21" t="n">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="AK8" s="21" t="n">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="AL8" s="20" t="inlineStr">
         <is>
@@ -2122,13 +2819,13 @@
         <v>-0.15</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>3</v>
+        <v>0.03</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>18</v>
+        <v>0.18</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="O9" s="18" t="n"/>
       <c r="P9" s="23" t="n"/>
@@ -2147,16 +2844,16 @@
         <v>16000</v>
       </c>
       <c r="W9" s="19" t="n">
-        <v>22</v>
+        <v>0.22</v>
       </c>
       <c r="X9" s="19" t="n">
-        <v>45</v>
+        <v>0.45</v>
       </c>
       <c r="Y9" s="19" t="n">
         <v>650000</v>
       </c>
       <c r="Z9" s="19" t="n">
-        <v>40</v>
+        <v>0.4</v>
       </c>
       <c r="AA9" s="18" t="inlineStr">
         <is>
@@ -2179,10 +2876,10 @@
         </is>
       </c>
       <c r="AE9" s="19" t="n">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="AF9" s="19" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="AG9" s="19" t="n">
         <v>45</v>
@@ -3977,7 +4674,7 @@
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="AL1"/>
   </mergeCells>
-  <dataValidations count="7">
+  <dataValidations count="22">
     <dataValidation sqref="C5:C53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Reference_Lists!$A$2:$A$15</formula1>
     </dataValidation>
@@ -3999,8 +4696,54 @@
     <dataValidation sqref="F5:F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
+    <dataValidation sqref="G5:G53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Rate" error="Enter a number greater than 0. No ₦ symbol or commas." promptTitle="Contracted Rate (₦)" prompt="Rate per trip in Naira. Must be greater than zero. No commas." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H5:H53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Cost" error="Enter a number greater than 0. No ₦ symbol or commas." promptTitle="Fully-Loaded Cost (₦)" prompt="Total all-in cost per trip in Naira. Must be greater than zero." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I5:I53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Distance" error="Enter a number greater than 0." promptTitle="Distance (km)" prompt="One-way route distance in kilometres." type="decimal" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="AI5:AI53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Trip Count" error="Enter a whole number greater than 0." promptTitle="Monthly Trips" prompt="Average number of trips per month." type="whole" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="L5:L53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="M5:M53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="N5:N53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="R5:R53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="W5:W53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="X5:X53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z5:Z53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="AE5:AE53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="AF5:AF53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="AJ5:AJ53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
+    <dataValidation sqref="AK5:AK53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Use Decimal Format" error="Enter as decimal (e.g. 0.25 for 25%). Do NOT enter 25." promptTitle="Rate/Percentage Field" prompt="Enter as DECIMAL (0.25 = 25%). Range: -1.0 to 5.0." type="decimal">
+      <formula1>-1</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -4022,339 +4765,339 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>Route Region</t>
         </is>
       </c>
-      <c r="B1" s="28" t="inlineStr">
+      <c r="B1" s="50" t="inlineStr">
         <is>
           <t>Cargo Type</t>
         </is>
       </c>
-      <c r="C1" s="28" t="inlineStr">
+      <c r="C1" s="50" t="inlineStr">
         <is>
           <t>Contract Type</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D1" s="50" t="inlineStr">
         <is>
           <t>Truck Type</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E1" s="50" t="inlineStr">
         <is>
           <t>Fuel Surcharge</t>
         </is>
       </c>
-      <c r="F1" s="28" t="inlineStr">
+      <c r="F1" s="50" t="inlineStr">
         <is>
           <t>Operating Region</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="51" t="inlineStr">
         <is>
           <t>North-South Corridor</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="51" t="inlineStr">
         <is>
           <t>General Cargo</t>
         </is>
       </c>
-      <c r="C2" s="29" t="inlineStr">
+      <c r="C2" s="51" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
       </c>
-      <c r="D2" s="29" t="inlineStr">
+      <c r="D2" s="51" t="inlineStr">
         <is>
           <t>10-Tonne</t>
         </is>
       </c>
-      <c r="E2" s="29" t="inlineStr">
+      <c r="E2" s="51" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F2" s="29" t="inlineStr">
+      <c r="F2" s="51" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="52" t="inlineStr">
         <is>
           <t>East-West Corridor</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="52" t="inlineStr">
         <is>
           <t>Container (20ft)</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="52" t="inlineStr">
         <is>
           <t>Dedicated</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="52" t="inlineStr">
         <is>
           <t>20-Tonne</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="52" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="52" t="inlineStr">
         <is>
           <t>Abuja</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="51" t="inlineStr">
         <is>
           <t>Lagos-North</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
         <is>
           <t>Container (40ft)</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>Contracted</t>
         </is>
       </c>
-      <c r="D4" s="29" t="inlineStr">
+      <c r="D4" s="51" t="inlineStr">
         <is>
           <t>30-Tonne</t>
         </is>
       </c>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr">
+      <c r="F4" s="51" t="inlineStr">
         <is>
           <t>Kano</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="52" t="inlineStr">
         <is>
           <t>Lagos-East</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>Bulk / Loose</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>Ad-hoc</t>
         </is>
       </c>
-      <c r="D5" s="30" t="inlineStr">
+      <c r="D5" s="52" t="inlineStr">
         <is>
           <t>40-Tonne</t>
         </is>
       </c>
-      <c r="F5" s="30" t="inlineStr">
+      <c r="F5" s="52" t="inlineStr">
         <is>
           <t>Port Harcourt</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>Lagos-West</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
         <is>
           <t>Cold Chain</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>Backhaul</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="51" t="inlineStr">
         <is>
           <t>Trailer</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="F6" s="51" t="inlineStr">
         <is>
           <t>Ibadan</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>South-South</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>Hazmat</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="52" t="inlineStr">
         <is>
           <t>Inter-modal</t>
         </is>
       </c>
-      <c r="D7" s="30" t="inlineStr">
+      <c r="D7" s="52" t="inlineStr">
         <is>
           <t>Flatbed</t>
         </is>
       </c>
-      <c r="F7" s="30" t="inlineStr">
+      <c r="F7" s="52" t="inlineStr">
         <is>
           <t>Onitsha</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>South-East</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="51" t="inlineStr">
         <is>
           <t>Project Cargo</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="51" t="inlineStr">
         <is>
           <t>Tanker</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="F8" s="51" t="inlineStr">
         <is>
           <t>Owerri</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="52" t="inlineStr">
         <is>
           <t>North-Central</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="52" t="inlineStr">
         <is>
           <t>Flatbed</t>
         </is>
       </c>
-      <c r="D9" s="30" t="inlineStr">
+      <c r="D9" s="52" t="inlineStr">
         <is>
           <t>Refrigerated</t>
         </is>
       </c>
-      <c r="F9" s="30" t="inlineStr">
+      <c r="F9" s="52" t="inlineStr">
         <is>
           <t>Enugu</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="51" t="inlineStr">
         <is>
           <t>North-East</t>
         </is>
       </c>
-      <c r="F10" s="29" t="inlineStr">
+      <c r="F10" s="51" t="inlineStr">
         <is>
           <t>Benin City</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>North-West</t>
         </is>
       </c>
-      <c r="F11" s="30" t="inlineStr">
+      <c r="F11" s="52" t="inlineStr">
         <is>
           <t>Kaduna</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>Cross-Country</t>
         </is>
       </c>
-      <c r="F12" s="29" t="inlineStr">
+      <c r="F12" s="51" t="inlineStr">
         <is>
           <t>Jos</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>Intra-City</t>
         </is>
       </c>
-      <c r="F13" s="30" t="inlineStr">
+      <c r="F13" s="52" t="inlineStr">
         <is>
           <t>Maiduguri</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>Port Drayage</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="51" t="inlineStr">
         <is>
           <t>Warri</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>Last Mile</t>
         </is>
       </c>
-      <c r="F15" s="30" t="inlineStr">
+      <c r="F15" s="52" t="inlineStr">
         <is>
           <t>Calabar</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" s="51" t="inlineStr">
         <is>
           <t>Aba</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="F17" s="30" t="inlineStr">
+      <c r="F17" s="52" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
@@ -4371,874 +5114,544 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>Field Key</t>
-        </is>
-      </c>
-      <c r="B1" s="28" t="inlineStr">
-        <is>
-          <t>Description / Tip</t>
-        </is>
-      </c>
-      <c r="C1" s="28" t="inlineStr">
-        <is>
-          <t>Example</t>
-        </is>
-      </c>
-      <c r="D1" s="28" t="inlineStr">
-        <is>
-          <t>REQ/OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="31" t="inlineStr">
-        <is>
-          <t>lane_id</t>
-        </is>
-      </c>
-      <c r="B2" s="32" t="inlineStr">
-        <is>
-          <t>Unique lane identifier — must be unique per period.</t>
-        </is>
-      </c>
-      <c r="C2" s="32" t="inlineStr">
-        <is>
-          <t>LN-001</t>
-        </is>
-      </c>
-      <c r="D2" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>lane_name</t>
-        </is>
-      </c>
-      <c r="B3" s="32" t="inlineStr">
-        <is>
-          <t>Human-readable lane name, e.g. origin–destination.</t>
-        </is>
-      </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>Lagos–Kano</t>
-        </is>
-      </c>
-      <c r="D3" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>route_region</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>Corridor classification from the Route Region list.</t>
-        </is>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>Lagos-North</t>
-        </is>
-      </c>
-      <c r="D4" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>cargo_type</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Type of cargo carried — from Cargo Type list.</t>
-        </is>
-      </c>
-      <c r="C5" s="32" t="inlineStr">
-        <is>
-          <t>General Cargo</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>fleet_division</t>
-        </is>
-      </c>
-      <c r="B6" s="32" t="inlineStr">
-        <is>
-          <t>Internal fleet division or cost centre.</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>Northern Fleet</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>Y = include in analysis, N = exclude. Required.</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>contracted_rate_ngn</t>
-        </is>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>Agreed rate per trip in Naira (no commas).</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>1,360,000</t>
-        </is>
-      </c>
-      <c r="D8" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>fully_loaded_cost_ngn</t>
-        </is>
-      </c>
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>Total all-in cost per trip: fuel + driver + maintenance + tolls + overheads.</t>
-        </is>
-      </c>
-      <c r="C9" s="32" t="inlineStr">
-        <is>
-          <t>1,020,000</t>
-        </is>
-      </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>distance_km</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>One-way distance in kilometres.</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="inlineStr">
-        <is>
-          <t>1,080</t>
-        </is>
-      </c>
-      <c r="D10" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>market_rate_ngn</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
-        <is>
-          <t>Current spot/market rate for this lane (optional but improves P1).</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t>1,400,000</t>
-        </is>
-      </c>
-      <c r="D11" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>rate_sensitivity</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>Elasticity: % change in trips per 1% rate change. Negative = trips fall as rate rises.</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="D12" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>proposed_rate_change_pct</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>Intended rate adjustment in %. Positive = increase.</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>min_margin_floor_pct</t>
-        </is>
-      </c>
-      <c r="B14" s="32" t="inlineStr">
-        <is>
-          <t>Minimum acceptable margin % for this lane.</t>
-        </is>
-      </c>
-      <c r="C14" s="32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D14" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
-        <is>
-          <t>rate_headroom_pct</t>
-        </is>
-      </c>
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>Estimated room to raise rate above current contracted level.</t>
-        </is>
-      </c>
-      <c r="C15" s="32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D15" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>return_lane_id</t>
-        </is>
-      </c>
-      <c r="B16" s="32" t="inlineStr">
-        <is>
-          <t>Lane ID of the paired return leg for backhaul pairing.</t>
-        </is>
-      </c>
-      <c r="C16" s="32" t="inlineStr">
-        <is>
-          <t>LN-002</t>
-        </is>
-      </c>
-      <c r="D16" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>backhaul_rate_ngn</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="inlineStr">
-        <is>
-          <t>Revenue on return leg (₦).</t>
-        </is>
-      </c>
-      <c r="C17" s="32" t="inlineStr">
-        <is>
-          <t>860,000</t>
-        </is>
-      </c>
-      <c r="D17" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
-        <is>
-          <t>backhaul_cost_ngn</t>
-        </is>
-      </c>
-      <c r="B18" s="32" t="inlineStr">
-        <is>
-          <t>Cost of return leg (₦).</t>
-        </is>
-      </c>
-      <c r="C18" s="32" t="inlineStr">
-        <is>
-          <t>680,000</t>
-        </is>
-      </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
-        <is>
-          <t>backhaul_recovery_pct</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="inlineStr">
-        <is>
-          <t>% of return trips carrying paying cargo.</t>
-        </is>
-      </c>
-      <c r="C19" s="32" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D19" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
-        <is>
-          <t>fuel_cost_per_km</t>
-        </is>
-      </c>
-      <c r="B20" s="32" t="inlineStr">
-        <is>
-          <t>Diesel cost per kilometre for this lane.</t>
-        </is>
-      </c>
-      <c r="C20" s="32" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="D20" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>driver_cost_per_trip</t>
-        </is>
-      </c>
-      <c r="B21" s="32" t="inlineStr">
-        <is>
-          <t>Driver wages + per diem allocated per trip.</t>
-        </is>
-      </c>
-      <c r="C21" s="32" t="inlineStr">
-        <is>
-          <t>85,000</t>
-        </is>
-      </c>
-      <c r="D21" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>maintenance_cost_per_trip</t>
-        </is>
-      </c>
-      <c r="B22" s="32" t="inlineStr">
-        <is>
-          <t>Tyres, servicing, and depreciation per trip.</t>
-        </is>
-      </c>
-      <c r="C22" s="32" t="inlineStr">
-        <is>
-          <t>62,000</t>
-        </is>
-      </c>
-      <c r="D22" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>toll_levy_per_trip</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="inlineStr">
-        <is>
-          <t>Checkpoints, state levies, and park fees per trip.</t>
-        </is>
-      </c>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>22,000</t>
-        </is>
-      </c>
-      <c r="D23" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>cost_inflation_pct</t>
-        </is>
-      </c>
-      <c r="B24" s="32" t="inlineStr">
-        <is>
-          <t>Percentage increase in operating costs year-on-year.</t>
-        </is>
-      </c>
-      <c r="C24" s="32" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>pass_through_rate</t>
-        </is>
-      </c>
-      <c r="B25" s="32" t="inlineStr">
-        <is>
-          <t>% of cost increase recovered via rate adjustment.</t>
-        </is>
-      </c>
-      <c r="C25" s="32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D25" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>prior_period_cost_ngn</t>
-        </is>
-      </c>
-      <c r="B26" s="32" t="inlineStr">
-        <is>
-          <t>Fully-loaded cost per trip in the previous period.</t>
-        </is>
-      </c>
-      <c r="C26" s="32" t="inlineStr">
-        <is>
-          <t>865,000</t>
-        </is>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="31" t="inlineStr">
-        <is>
-          <t>fx_exposure_pct</t>
-        </is>
-      </c>
-      <c r="B27" s="32" t="inlineStr">
-        <is>
-          <t>% of operating costs linked to FX (diesel, parts imports).</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D27" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>truck_id</t>
-        </is>
-      </c>
-      <c r="B28" s="32" t="inlineStr">
-        <is>
-          <t>Asset registration number or fleet ID.</t>
-        </is>
-      </c>
-      <c r="C28" s="32" t="inlineStr">
-        <is>
-          <t>TRK-045</t>
-        </is>
-      </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
-        <is>
-          <t>truck_type</t>
-        </is>
-      </c>
-      <c r="B29" s="32" t="inlineStr">
-        <is>
-          <t>Truck class from the Truck Type list.</t>
-        </is>
-      </c>
-      <c r="C29" s="32" t="inlineStr">
-        <is>
-          <t>30-Tonne</t>
-        </is>
-      </c>
-      <c r="D29" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="31" t="inlineStr">
-        <is>
-          <t>contract_type</t>
-        </is>
-      </c>
-      <c r="B30" s="32" t="inlineStr">
-        <is>
-          <t>Spot / Dedicated / Contracted / Ad-hoc / Backhaul.</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="inlineStr">
-        <is>
-          <t>Contracted</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>customer_name</t>
-        </is>
-      </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>Shipper or client name.</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>Dangote Industries</t>
-        </is>
-      </c>
-      <c r="D31" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>customer_margin_pct</t>
-        </is>
-      </c>
-      <c r="B32" s="32" t="inlineStr">
-        <is>
-          <t>Customer contribution margin allocation %.</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D32" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>rebate_pct</t>
-        </is>
-      </c>
-      <c r="B33" s="32" t="inlineStr">
-        <is>
-          <t>Volume rebate % if applicable.</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="D33" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="31" t="inlineStr">
-        <is>
-          <t>payment_terms_days</t>
-        </is>
-      </c>
-      <c r="B34" s="32" t="inlineStr">
-        <is>
-          <t>Standard payment cycle in days.</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>fuel_surcharge_clause</t>
-        </is>
-      </c>
-      <c r="B35" s="32" t="inlineStr">
-        <is>
-          <t>Whether contract includes automatic fuel surcharge passthrough.</t>
-        </is>
-      </c>
-      <c r="C35" s="32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D35" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="31" t="inlineStr">
-        <is>
-          <t>monthly_trips</t>
-        </is>
-      </c>
-      <c r="B36" s="32" t="inlineStr">
-        <is>
-          <t>Number of trips per month on this lane. Required.</t>
-        </is>
-      </c>
-      <c r="C36" s="32" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D36" s="33" t="inlineStr">
-        <is>
-          <t>REQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="31" t="inlineStr">
-        <is>
-          <t>discount_depth_pct</t>
-        </is>
-      </c>
-      <c r="B37" s="32" t="inlineStr">
-        <is>
-          <t>Volume discount offered (% of contracted rate).</t>
-        </is>
-      </c>
-      <c r="C37" s="32" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D37" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
-        <is>
-          <t>volume_response_pct</t>
-        </is>
-      </c>
-      <c r="B38" s="32" t="inlineStr">
-        <is>
-          <t>% volume change expected from rate adjustment.</t>
-        </is>
-      </c>
-      <c r="C38" s="32" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D38" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="31" t="inlineStr">
-        <is>
-          <t>operating_region</t>
-        </is>
-      </c>
-      <c r="B39" s="32" t="inlineStr">
-        <is>
-          <t>Primary operating hub region.</t>
-        </is>
-      </c>
-      <c r="C39" s="32" t="inlineStr">
-        <is>
-          <t>Lagos</t>
-        </is>
-      </c>
-      <c r="D39" s="34" t="inlineStr">
-        <is>
-          <t>OPT</t>
-        </is>
-      </c>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="53" t="n"/>
+      <c r="B1" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  VALIDATION RULES  ·  Logistics  ·  What the platform checks on upload</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="13" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="n"/>
+      <c r="B2" s="53" t="n"/>
+      <c r="C2" s="53" t="n"/>
+      <c r="D2" s="53" t="n"/>
+    </row>
+    <row r="3" ht="15.8" customHeight="1">
+      <c r="A3" s="53" t="n"/>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PASS 1 - STRUCTURAL VALIDATION  (hard stops — upload cannot proceed if any fail)</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="n"/>
+      <c r="D3" s="12" t="n"/>
+      <c r="E3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="53" t="n"/>
+      <c r="B4" s="56" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="C4" s="56" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="D4" s="56" t="inlineStr">
+        <is>
+          <t>WHAT WE CHECK</t>
+        </is>
+      </c>
+      <c r="E4" s="57" t="inlineStr">
+        <is>
+          <t>CORRECTIVE ACTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="53" t="n"/>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>File format</t>
+        </is>
+      </c>
+      <c r="C5" s="59" t="inlineStr">
+        <is>
+          <t>HARD STOP</t>
+        </is>
+      </c>
+      <c r="D5" s="58" t="inlineStr">
+        <is>
+          <t>File must be .xlsx or .csv</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>Re-save the file as .xlsx from Excel before uploading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="53" t="n"/>
+      <c r="B6" s="58" t="inlineStr">
+        <is>
+          <t>Required columns</t>
+        </is>
+      </c>
+      <c r="C6" s="59" t="inlineStr">
+        <is>
+          <t>HARD STOP</t>
+        </is>
+      </c>
+      <c r="D6" s="58" t="inlineStr">
+        <is>
+          <t>Lane Data sheet must exist and contain all required column names in exact API format</t>
+        </is>
+      </c>
+      <c r="E6" s="48" t="inlineStr">
+        <is>
+          <t>Do not rename or delete columns. Use the template as issued.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="53" t="n"/>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Required fields</t>
+        </is>
+      </c>
+      <c r="C7" s="59" t="inlineStr">
+        <is>
+          <t>HARD STOP</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>lane_id, lane_name, route_region, cargo_type, active, contracted_rate_ngn, fully_loaded_cost_ngn, distance_km, contract_type, monthly_trips must not be blank</t>
+        </is>
+      </c>
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>Complete all yellow cells for every lane row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="53" t="n"/>
+      <c r="B8" s="58" t="inlineStr">
+        <is>
+          <t>Unique Lane IDs</t>
+        </is>
+      </c>
+      <c r="C8" s="59" t="inlineStr">
+        <is>
+          <t>HARD STOP</t>
+        </is>
+      </c>
+      <c r="D8" s="58" t="inlineStr">
+        <is>
+          <t>No duplicate lane_id values within the same upload</t>
+        </is>
+      </c>
+      <c r="E8" s="48" t="inlineStr">
+        <is>
+          <t>Each lane row must have a unique ID. Rename duplicates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="53" t="n"/>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>Numeric fields</t>
+        </is>
+      </c>
+      <c r="C9" s="59" t="inlineStr">
+        <is>
+          <t>HARD STOP</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>contracted_rate_ngn, fully_loaded_cost_ngn, distance_km, monthly_trips must be numeric and greater than zero</t>
+        </is>
+      </c>
+      <c r="E9" s="48" t="inlineStr">
+        <is>
+          <t>Remove ₦ symbols and commas. Enter numbers only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="53" t="n"/>
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>Controlled vocabulary</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>HARD STOP</t>
+        </is>
+      </c>
+      <c r="D10" s="58" t="inlineStr">
+        <is>
+          <t>route_region, cargo_type, contract_type, truck_type must match Reference_Lists values exactly (case-sensitive)</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="inlineStr">
+        <is>
+          <t>Use dropdown selections — do not free-type. See Reference_Lists tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="53" t="n"/>
+      <c r="B11" s="53" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="53" t="n"/>
+      <c r="B12" s="53" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
+    </row>
+    <row r="13" ht="15.8" customHeight="1">
+      <c r="A13" s="53" t="n"/>
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PASS 2 - SEMANTIC VALIDATION  (warnings — review and confirm or correct before analysis runs)</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="53" t="n"/>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>CHECK</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>SEVERITY</t>
+        </is>
+      </c>
+      <c r="D14" s="56" t="inlineStr">
+        <is>
+          <t>WHAT WE CHECK</t>
+        </is>
+      </c>
+      <c r="E14" s="57" t="inlineStr">
+        <is>
+          <t>CORRECTIVE ACTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="53" t="n"/>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>Rate &lt; Cost inversion</t>
+        </is>
+      </c>
+      <c r="C15" s="61" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="D15" s="58" t="inlineStr">
+        <is>
+          <t>contracted_rate_ngn &lt; fully_loaded_cost_ngn — lane is loss-making on every trip. Common data entry error.</t>
+        </is>
+      </c>
+      <c r="E15" s="48" t="inlineStr">
+        <is>
+          <t>Verify contracted rate and fully-loaded cost. Check for units mismatch (per-trip vs per-km).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="53" t="n"/>
+      <c r="B16" s="58" t="inlineStr">
+        <is>
+          <t>Implausible margin</t>
+        </is>
+      </c>
+      <c r="C16" s="61" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="D16" s="58" t="inlineStr">
+        <is>
+          <t>Lane margin &gt; 60% or &lt; 0%. Unusual but not impossible.</t>
+        </is>
+      </c>
+      <c r="E16" s="48" t="inlineStr">
+        <is>
+          <t>Confirm rate and cost figures with finance or fleet ops team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="53" t="n"/>
+      <c r="B17" s="58" t="inlineStr">
+        <is>
+          <t>Distance outlier</t>
+        </is>
+      </c>
+      <c r="C17" s="61" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="D17" s="58" t="inlineStr">
+        <is>
+          <t>distance_km &gt; 2000km or &lt; 10km. Likely data entry error.</t>
+        </is>
+      </c>
+      <c r="E17" s="48" t="inlineStr">
+        <is>
+          <t>Check whether distance is entered in km, not metres or miles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="53" t="n"/>
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>Monthly trips outlier</t>
+        </is>
+      </c>
+      <c r="C18" s="61" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="D18" s="58" t="inlineStr">
+        <is>
+          <t>monthly_trips &gt; 200 or &lt; 1. Likely incorrect.</t>
+        </is>
+      </c>
+      <c r="E18" s="48" t="inlineStr">
+        <is>
+          <t>Confirm trip count is per month, not per week or per year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="53" t="n"/>
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>Cost inflation &gt; 100%</t>
+        </is>
+      </c>
+      <c r="C19" s="61" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="D19" s="58" t="inlineStr">
+        <is>
+          <t>cost_inflation_pct entered as &gt; 1.0 — may have been entered as integer (e.g. 18 instead of 0.18).</t>
+        </is>
+      </c>
+      <c r="E19" s="48" t="inlineStr">
+        <is>
+          <t>All percentages must be entered as decimals. 18% = 0.18, not 18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="53" t="n"/>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>Pass-through &gt; 100%</t>
+        </is>
+      </c>
+      <c r="C20" s="61" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="D20" s="58" t="inlineStr">
+        <is>
+          <t>pass_through_rate &gt; 1.0 — may have been entered as integer.</t>
+        </is>
+      </c>
+      <c r="E20" s="48" t="inlineStr">
+        <is>
+          <t>All percentages must be entered as decimals. 65% = 0.65, not 65.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="53" t="n"/>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>Lane ID drift</t>
+        </is>
+      </c>
+      <c r="C21" s="61" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+      <c r="D21" s="58" t="inlineStr">
+        <is>
+          <t>Lane IDs in prior upload not found in current upload.</t>
+        </is>
+      </c>
+      <c r="E21" s="48" t="inlineStr">
+        <is>
+          <t>Confirm lane was decommissioned, not accidentally renamed. Renamed lanes break time-series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="53" t="n"/>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>New lanes detected</t>
+        </is>
+      </c>
+      <c r="C22" s="62" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D22" s="58" t="inlineStr">
+        <is>
+          <t>Lane IDs in current upload not found in prior upload.</t>
+        </is>
+      </c>
+      <c r="E22" s="48" t="inlineStr">
+        <is>
+          <t>Confirm these are genuinely new lanes. Platform will begin tracking from this period.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="53" t="n"/>
+      <c r="B23" s="53" t="n"/>
+      <c r="C23" s="53" t="n"/>
+      <c r="D23" s="53" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="53" t="n"/>
+      <c r="B24" s="53" t="n"/>
+      <c r="C24" s="53" t="n"/>
+      <c r="D24" s="53" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="53" t="n"/>
+      <c r="B25" s="53" t="n"/>
+      <c r="C25" s="53" t="n"/>
+      <c r="D25" s="53" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="53" t="n"/>
+      <c r="B26" s="53" t="n"/>
+      <c r="C26" s="53" t="n"/>
+      <c r="D26" s="53" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="53" t="n"/>
+      <c r="B27" s="53" t="n"/>
+      <c r="C27" s="53" t="n"/>
+      <c r="D27" s="53" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="53" t="n"/>
+      <c r="B28" s="53" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="53" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="53" t="n"/>
+      <c r="B29" s="53" t="n"/>
+      <c r="C29" s="53" t="n"/>
+      <c r="D29" s="53" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="53" t="n"/>
+      <c r="B30" s="53" t="n"/>
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="53" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="53" t="n"/>
+      <c r="B31" s="53" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="53" t="n"/>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="53" t="n"/>
+      <c r="B33" s="53" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="53" t="n"/>
+      <c r="B34" s="53" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="53" t="n"/>
+      <c r="B35" s="53" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="53" t="n"/>
+      <c r="B36" s="53" t="n"/>
+      <c r="C36" s="53" t="n"/>
+      <c r="D36" s="53" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="53" t="n"/>
+      <c r="B37" s="53" t="n"/>
+      <c r="C37" s="53" t="n"/>
+      <c r="D37" s="53" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="53" t="n"/>
+      <c r="B38" s="53" t="n"/>
+      <c r="C38" s="53" t="n"/>
+      <c r="D38" s="53" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="53" t="n"/>
+      <c r="B39" s="53" t="n"/>
+      <c r="C39" s="53" t="n"/>
+      <c r="D39" s="53" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B3:E3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
+++ b/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
@@ -304,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -437,6 +437,18 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,9 +565,9 @@
       <text>
         <t>Cargo Type
 ──────────────────────────────
-Type of cargo carried. Must match Reference_Lists.
+Type of cargo carried on this lane. Must match Reference_Lists exactly.
 Format: Select from dropdown
-Example: General Cargo · Cold Chain · Container (20ft)
+Options: General Cargo · Container (20ft) · Container (40ft) · Bulk / Loose · Cold Chain · Hazmat · Project Cargo · Flatbed · Passengers
 Required: YES</t>
       </text>
     </comment>
@@ -793,9 +805,10 @@
       <text>
         <t>Truck Type
 ──────────────────────────────
-Vehicle class. Must match Reference_Lists.
+Truck / vehicle class for this lane. Must match Reference_Lists.
 Format: Select from dropdown
-Example: 30-Tonne · Refrigerated · Flatbed · Tanker
+Options: Pickup / Van · Hiace Bus · Coaster Bus · 10-Tonne · 20-Tonne · 30-Tonne · 40-Tonne · Trailer · Flatbed · Tanker · Refrigerated · Luxury Bus · Sedan / SUV · Mini Bus
+Used for asset-class cost benchmarks.
 Required: NO</t>
       </text>
     </comment>
@@ -1416,7 +1429,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="B22" s="40" t="inlineStr">
         <is>
@@ -22619,7 +22631,7 @@
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="AL1"/>
   </mergeCells>
-  <dataValidations count="7">
+  <dataValidations count="12">
     <dataValidation sqref="F5:F504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
@@ -22641,6 +22653,21 @@
     <dataValidation sqref="A5:A504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Duplicate ID" error="This ID already exists in column A. Each row must have a unique ID." type="custom" errorStyle="stop">
       <formula1>COUNTIF($A$5:$A$504,A5)=1</formula1>
     </dataValidation>
+    <dataValidation sqref="C5:C504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Route Region" error="Value must match a Route Region in the Reference_Lists sheet." type="list" errorStyle="warning">
+      <formula1>=Reference_Lists!$A$2:$A$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Cargo Type" error="Value must match a Cargo Type in the Reference_Lists sheet." type="list" errorStyle="warning">
+      <formula1>=Reference_Lists!$B$2:$B$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB5:AB504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Truck Type" error="Value must match a Truck Type in the Reference_Lists sheet." type="list" errorStyle="warning">
+      <formula1>=Reference_Lists!$D$2:$D$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="AC5:AC504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Contract Type" error="Value must match a Contract Type in the Reference_Lists sheet." type="list" errorStyle="warning">
+      <formula1>=Reference_Lists!$C$2:$C$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="AL5:AL504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Operating Region" error="Value must match an Operating Region in the Reference_Lists sheet." type="list" errorStyle="warning">
+      <formula1>=Reference_Lists!$F$2:$F$17</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -22653,7 +22680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="37" min="1" max="6"/>
@@ -22707,9 +22734,9 @@
           <t>Spot</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
-        <is>
-          <t>10-Tonne</t>
+      <c r="D2" s="48" t="inlineStr">
+        <is>
+          <t>Pickup / Van</t>
         </is>
       </c>
       <c r="E2" s="27" t="inlineStr">
@@ -22739,9 +22766,9 @@
           <t>Dedicated</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
-        <is>
-          <t>20-Tonne</t>
+      <c r="D3" s="49" t="inlineStr">
+        <is>
+          <t>Hiace Bus</t>
         </is>
       </c>
       <c r="E3" s="28" t="inlineStr">
@@ -22771,9 +22798,9 @@
           <t>Contracted</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
-        <is>
-          <t>30-Tonne</t>
+      <c r="D4" s="48" t="inlineStr">
+        <is>
+          <t>Coaster Bus</t>
         </is>
       </c>
       <c r="E4" s="27" t="inlineStr">
@@ -22803,9 +22830,9 @@
           <t>Ad-hoc</t>
         </is>
       </c>
-      <c r="D5" s="28" t="inlineStr">
-        <is>
-          <t>40-Tonne</t>
+      <c r="D5" s="49" t="inlineStr">
+        <is>
+          <t>10-Tonne</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -22830,9 +22857,9 @@
           <t>Backhaul</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>Trailer</t>
+      <c r="D6" s="48" t="inlineStr">
+        <is>
+          <t>20-Tonne</t>
         </is>
       </c>
       <c r="F6" s="27" t="inlineStr">
@@ -22857,9 +22884,9 @@
           <t>Inter-modal</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
-        <is>
-          <t>Flatbed</t>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>30-Tonne</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
@@ -22879,9 +22906,9 @@
           <t>Project Cargo</t>
         </is>
       </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>Tanker</t>
+      <c r="D8" s="48" t="inlineStr">
+        <is>
+          <t>40-Tonne</t>
         </is>
       </c>
       <c r="F8" s="27" t="inlineStr">
@@ -22901,9 +22928,9 @@
           <t>Flatbed</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>Refrigerated</t>
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>Trailer</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -22918,6 +22945,16 @@
           <t>North-East</t>
         </is>
       </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>Passengers</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>Flatbed</t>
+        </is>
+      </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
           <t>Benin City</t>
@@ -22930,6 +22967,11 @@
           <t>North-West</t>
         </is>
       </c>
+      <c r="D11" s="50" t="inlineStr">
+        <is>
+          <t>Tanker</t>
+        </is>
+      </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
           <t>Kaduna</t>
@@ -22942,6 +22984,11 @@
           <t>Cross-Country</t>
         </is>
       </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>Refrigerated</t>
+        </is>
+      </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
           <t>Jos</t>
@@ -22954,6 +23001,11 @@
           <t>Intra-City</t>
         </is>
       </c>
+      <c r="D13" s="50" t="inlineStr">
+        <is>
+          <t>Luxury Bus</t>
+        </is>
+      </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
           <t>Maiduguri</t>
@@ -22966,6 +23018,11 @@
           <t>Port Drayage</t>
         </is>
       </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>Sedan / SUV</t>
+        </is>
+      </c>
       <c r="F14" s="27" t="inlineStr">
         <is>
           <t>Warri</t>
@@ -22978,6 +23035,11 @@
           <t>Last Mile</t>
         </is>
       </c>
+      <c r="D15" s="50" t="inlineStr">
+        <is>
+          <t>Mini Bus</t>
+        </is>
+      </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
           <t>Calabar</t>
@@ -22998,6 +23060,9 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
+++ b/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
@@ -22680,7 +22680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="37" min="1" max="6"/>
@@ -23060,9 +23060,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
+++ b/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
@@ -22631,7 +22631,7 @@
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="AL1"/>
   </mergeCells>
-  <dataValidations count="12">
+  <dataValidations count="13">
     <dataValidation sqref="F5:F504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
@@ -22668,6 +22668,9 @@
     <dataValidation sqref="AL5:AL504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Operating Region" error="Value must match an Operating Region in the Reference_Lists sheet." type="list" errorStyle="warning">
       <formula1>=Reference_Lists!$F$2:$F$17</formula1>
     </dataValidation>
+    <dataValidation sqref="AH5:AH504" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Fuel Surcharge Clause" error="Please select from the dropdown list." promptTitle="Fuel Surcharge Clause" prompt="Does this contract include automatic fuel surcharge passthrough? Select Yes, No, or Partial." type="list" errorStyle="warning">
+      <formula1>=Reference_Lists!$E$2:$E$4</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
+++ b/public/downloads/MarginCOS_Data_Template_v3.2_Logistics.xlsx
@@ -1982,12 +1982,12 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Contracted Rate (₦)</t>
+          <t>Contracted Rate</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Fully-Loaded Cost (₦)</t>
+          <t>Fully-Loaded Cost</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Market Rate (₦)</t>
+          <t>Market Rate</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>Backhaul Rate (₦)</t>
+          <t>Backhaul Rate</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
         <is>
-          <t>Backhaul Cost (₦)</t>
+          <t>Backhaul Cost</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr">
@@ -2042,22 +2042,22 @@
       </c>
       <c r="S4" s="4" t="inlineStr">
         <is>
-          <t>Fuel Cost/km (₦)</t>
+          <t>Fuel Cost/km</t>
         </is>
       </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>Driver Cost/Trip (₦)</t>
+          <t>Driver Cost/Trip</t>
         </is>
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>Maintenance/Trip (₦)</t>
+          <t>Maintenance/Trip</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>Tolls &amp; Levies/Trip (₦)</t>
+          <t>Tolls &amp; Levies/Trip</t>
         </is>
       </c>
       <c r="W4" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y4" s="4" t="inlineStr">
         <is>
-          <t>Prior Period Cost (₦)</t>
+          <t>Prior Period Cost</t>
         </is>
       </c>
       <c r="Z4" s="4" t="inlineStr">
@@ -2144,17 +2144,17 @@
     <row r="5" ht="18" customHeight="1" s="37">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>LN-001</t>
+          <t>Lane-001</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Lagos–Kano</t>
+          <t>Metro A – Metro B</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Lagos-North</t>
+          <t>North Corridor</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AD5" s="5" t="inlineStr">
         <is>
-          <t>Dangote Industries</t>
+          <t>Partner A</t>
         </is>
       </c>
       <c r="AE5" s="6" t="n">
@@ -2279,24 +2279,24 @@
       </c>
       <c r="AL5" s="5" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Metro North A</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" s="37">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>LN-002</t>
+          <t>Lane-002</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Kano–Lagos</t>
+          <t>Metro B – Metro A</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Lagos-North</t>
+          <t>North Corridor</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="AD6" s="7" t="inlineStr">
         <is>
-          <t>Dangote Industries</t>
+          <t>Partner B</t>
         </is>
       </c>
       <c r="AE6" s="8" t="n">
@@ -2415,24 +2415,24 @@
       </c>
       <c r="AL6" s="7" t="inlineStr">
         <is>
-          <t>Kano</t>
+          <t>Metro North B</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" s="37">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>LN-003</t>
+          <t>Lane-003</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Lagos–Onitsha</t>
+          <t>Metro A – City East</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Lagos-East</t>
+          <t>East Corridor</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="AD7" s="5" t="inlineStr">
         <is>
-          <t>UAC Foods</t>
+          <t>Partner C</t>
         </is>
       </c>
       <c r="AE7" s="6" t="n">
@@ -2547,24 +2547,24 @@
       </c>
       <c r="AL7" s="5" t="inlineStr">
         <is>
-          <t>Lagos</t>
+          <t>Metro North A</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="37">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>LN-004</t>
+          <t>Lane-004</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Abuja–Kaduna</t>
+          <t>City C – City D</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>North-Central</t>
+          <t>Central Corridor</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="AD8" s="7" t="inlineStr">
         <is>
-          <t>Flour Mills Nigeria</t>
+          <t>Partner D</t>
         </is>
       </c>
       <c r="AE8" s="8" t="n">
@@ -2685,24 +2685,24 @@
       </c>
       <c r="AL8" s="7" t="inlineStr">
         <is>
-          <t>Abuja</t>
+          <t>City Central C</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" s="37">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>LN-005</t>
+          <t>Lane-005</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Port Harcourt–Lagos (Coastal)</t>
+          <t>Port – Metro A (Coastal)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>South-South</t>
+          <t>Coastal Route</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="AD9" s="5" t="inlineStr">
         <is>
-          <t>Nestle Nigeria</t>
+          <t>Partner E</t>
         </is>
       </c>
       <c r="AE9" s="6" t="n">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="AL9" s="5" t="inlineStr">
         <is>
-          <t>Port Harcourt</t>
+          <t>Port South</t>
         </is>
       </c>
     </row>
@@ -22683,7 +22683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="37" min="1" max="6"/>
@@ -22724,7 +22724,7 @@
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>North-South Corridor</t>
+          <t>North Corridor</t>
         </is>
       </c>
       <c r="B2" s="27" t="inlineStr">
@@ -22756,7 +22756,7 @@
     <row r="3">
       <c r="A3" s="28" t="inlineStr">
         <is>
-          <t>East-West Corridor</t>
+          <t>South Corridor</t>
         </is>
       </c>
       <c r="B3" s="28" t="inlineStr">
@@ -22781,14 +22781,14 @@
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Abuja</t>
+          <t>Nairobi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>Lagos-North</t>
+          <t>East Corridor</t>
         </is>
       </c>
       <c r="B4" s="27" t="inlineStr">
@@ -22813,14 +22813,14 @@
       </c>
       <c r="F4" s="27" t="inlineStr">
         <is>
-          <t>Kano</t>
+          <t>Johannesburg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="inlineStr">
         <is>
-          <t>Lagos-East</t>
+          <t>West Corridor</t>
         </is>
       </c>
       <c r="B5" s="28" t="inlineStr">
@@ -22840,14 +22840,14 @@
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>Port Harcourt</t>
+          <t>Accra</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>Lagos-West</t>
+          <t>Central Corridor</t>
         </is>
       </c>
       <c r="B6" s="27" t="inlineStr">
@@ -22867,14 +22867,14 @@
       </c>
       <c r="F6" s="27" t="inlineStr">
         <is>
-          <t>Ibadan</t>
+          <t>Dar es Salaam</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="28" t="inlineStr">
         <is>
-          <t>South-South</t>
+          <t>Coastal Route</t>
         </is>
       </c>
       <c r="B7" s="28" t="inlineStr">
@@ -22894,14 +22894,14 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Onitsha</t>
+          <t>Cairo</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>South-East</t>
+          <t>Cross-Border</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr">
@@ -22916,14 +22916,14 @@
       </c>
       <c r="F8" s="27" t="inlineStr">
         <is>
-          <t>Owerri</t>
+          <t>Casablanca</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="28" t="inlineStr">
         <is>
-          <t>North-Central</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B9" s="28" t="inlineStr">
@@ -22938,16 +22938,12 @@
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Enugu</t>
+          <t>Dubai</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>North-East</t>
-        </is>
-      </c>
+      <c r="A10" s="27" t="n"/>
       <c r="B10" s="50" t="inlineStr">
         <is>
           <t>Passengers</t>
@@ -22960,16 +22956,12 @@
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>Benin City</t>
+          <t>Mumbai</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>North-West</t>
-        </is>
-      </c>
+      <c r="A11" s="28" t="n"/>
       <c r="D11" s="50" t="inlineStr">
         <is>
           <t>Tanker</t>
@@ -22977,16 +22969,12 @@
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Kaduna</t>
+          <t>Singapore</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>Cross-Country</t>
-        </is>
-      </c>
+      <c r="A12" s="27" t="n"/>
       <c r="D12" s="51" t="inlineStr">
         <is>
           <t>Refrigerated</t>
@@ -22994,16 +22982,12 @@
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>Jos</t>
+          <t>London</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>Intra-City</t>
-        </is>
-      </c>
+      <c r="A13" s="28" t="n"/>
       <c r="D13" s="50" t="inlineStr">
         <is>
           <t>Luxury Bus</t>
@@ -23011,16 +22995,12 @@
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Maiduguri</t>
+          <t>São Paulo</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>Port Drayage</t>
-        </is>
-      </c>
+      <c r="A14" s="27" t="n"/>
       <c r="D14" s="51" t="inlineStr">
         <is>
           <t>Sedan / SUV</t>
@@ -23028,16 +23008,12 @@
       </c>
       <c r="F14" s="27" t="inlineStr">
         <is>
-          <t>Warri</t>
+          <t>Mexico City</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>Last Mile</t>
-        </is>
-      </c>
+      <c r="A15" s="28" t="n"/>
       <c r="D15" s="50" t="inlineStr">
         <is>
           <t>Mini Bus</t>
@@ -23045,14 +23021,14 @@
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Calabar</t>
+          <t>Jakarta</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="F16" s="27" t="inlineStr">
         <is>
-          <t>Aba</t>
+          <t>Manila</t>
         </is>
       </c>
     </row>
@@ -23063,6 +23039,15 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23247,7 +23232,7 @@
       </c>
       <c r="E9" s="39" t="inlineStr">
         <is>
-          <t>Remove ₦ symbols and commas. Enter numbers only.</t>
+          <t>Remove currency symbols and commas. Enter numbers only.</t>
         </is>
       </c>
     </row>
